--- a/samples/예시데이터_8월재고분석현황(대구).xlsx
+++ b/samples/예시데이터_8월재고분석현황(대구).xlsx
@@ -3,10 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="대구 8월 원자재" sheetId="1" r:id="rId1"/>
-    <sheet name="대구 7월 원자재" sheetId="2" r:id="rId2"/>
-    <sheet name="대구 8월 제품" sheetId="3" r:id="rId3"/>
-    <sheet name="대구 7월 제품" sheetId="4" r:id="rId4"/>
+    <sheet name="원자재" sheetId="1" r:id="rId1"/>
+    <sheet name="반제품" sheetId="2" r:id="rId2"/>
+    <sheet name="제품" sheetId="3" r:id="rId3"/>
+    <sheet name="대구 8월 원자재" sheetId="4" r:id="rId4"/>
+    <sheet name="대구 7월 원자재" sheetId="5" r:id="rId5"/>
+    <sheet name="대구 8월 반제품" sheetId="6" r:id="rId6"/>
+    <sheet name="대구 7월 반제품" sheetId="7" r:id="rId7"/>
+    <sheet name="대구 8월 제품" sheetId="8" r:id="rId8"/>
+    <sheet name="대구 7월 제품" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -400,6 +405,537 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K9"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>대구기준</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>구분</v>
+      </c>
+      <c r="B2" t="str">
+        <v>대분류</v>
+      </c>
+      <c r="C2" t="str">
+        <v>재고현황(07월)</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>재고현황(08월)</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>수량 증감 비교 (08월재고현황 - 07월재고현황)</v>
+      </c>
+      <c r="H2" t="str">
+        <v>금액 증감 비교 (08월재고현황 - 07월재고현황)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>원인분석</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>비고</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="D3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="E3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="F3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>07월 재고현황</v>
+      </c>
+      <c r="J3" t="str">
+        <v>08월 재고현황</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>원자재</v>
+      </c>
+      <c r="B4" t="str">
+        <v>하우징류</v>
+      </c>
+      <c r="C4">
+        <v>5000</v>
+      </c>
+      <c r="D4">
+        <v>600000</v>
+      </c>
+      <c r="E4">
+        <v>4200</v>
+      </c>
+      <c r="F4">
+        <v>504000</v>
+      </c>
+      <c r="G4">
+        <v>-800</v>
+      </c>
+      <c r="H4">
+        <v>-96000</v>
+      </c>
+      <c r="I4" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J4" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v>터미널류</v>
+      </c>
+      <c r="C5">
+        <v>30000</v>
+      </c>
+      <c r="D5">
+        <v>1350000</v>
+      </c>
+      <c r="E5">
+        <v>28000</v>
+      </c>
+      <c r="F5">
+        <v>1260000</v>
+      </c>
+      <c r="G5">
+        <v>-2000</v>
+      </c>
+      <c r="H5">
+        <v>-90000</v>
+      </c>
+      <c r="I5" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J5" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v>와이어류</v>
+      </c>
+      <c r="C6">
+        <v>7000</v>
+      </c>
+      <c r="D6">
+        <v>1260000</v>
+      </c>
+      <c r="E6">
+        <v>9000</v>
+      </c>
+      <c r="F6">
+        <v>1620000</v>
+      </c>
+      <c r="G6">
+        <v>2000</v>
+      </c>
+      <c r="H6">
+        <v>360000</v>
+      </c>
+      <c r="I6" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J6" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v>스위치</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>1000000</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>1250000</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>250000</v>
+      </c>
+      <c r="I7" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J7" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v>기타</v>
+      </c>
+      <c r="C8">
+        <v>600</v>
+      </c>
+      <c r="D8">
+        <v>186000</v>
+      </c>
+      <c r="E8">
+        <v>600</v>
+      </c>
+      <c r="F8">
+        <v>186000</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J8" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v>합계</v>
+      </c>
+      <c r="C9">
+        <v>42620</v>
+      </c>
+      <c r="D9">
+        <v>4396000</v>
+      </c>
+      <c r="E9">
+        <v>41825</v>
+      </c>
+      <c r="F9">
+        <v>4820000</v>
+      </c>
+      <c r="G9">
+        <v>-795</v>
+      </c>
+      <c r="H9">
+        <v>424000</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>대구기준</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>구분</v>
+      </c>
+      <c r="B2" t="str">
+        <v>07월 재고현황</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>08월 재고현황</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>재고잔량분석</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="C3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="D3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="E3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>예시고객사 3</v>
+      </c>
+      <c r="B4">
+        <v>300</v>
+      </c>
+      <c r="C4">
+        <v>750000</v>
+      </c>
+      <c r="D4">
+        <v>260</v>
+      </c>
+      <c r="E4">
+        <v>650000</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>예시고객사 1</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>90</v>
+      </c>
+      <c r="E5">
+        <v>360000</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>총합계</v>
+      </c>
+      <c r="B6">
+        <v>300</v>
+      </c>
+      <c r="C6">
+        <v>750000</v>
+      </c>
+      <c r="D6">
+        <v>350</v>
+      </c>
+      <c r="E6">
+        <v>1010000</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>대구기준</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>구분</v>
+      </c>
+      <c r="B2" t="str">
+        <v>07월 재고현황</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>08월 재고현황</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>재고잔량분석</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="C3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="D3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="E3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>예시고객사 3</v>
+      </c>
+      <c r="B4">
+        <v>75</v>
+      </c>
+      <c r="C4">
+        <v>2025000</v>
+      </c>
+      <c r="D4">
+        <v>75</v>
+      </c>
+      <c r="E4">
+        <v>2025000</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>예시고객사 1</v>
+      </c>
+      <c r="B5">
+        <v>200</v>
+      </c>
+      <c r="C5">
+        <v>1800000</v>
+      </c>
+      <c r="D5">
+        <v>150</v>
+      </c>
+      <c r="E5">
+        <v>1350000</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>총합계</v>
+      </c>
+      <c r="B6">
+        <v>275</v>
+      </c>
+      <c r="C6">
+        <v>3825000</v>
+      </c>
+      <c r="D6">
+        <v>225</v>
+      </c>
+      <c r="E6">
+        <v>3375000</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I7"/>
   <sheetData>
     <row r="1">
@@ -612,7 +1148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H7"/>
   <sheetData>
@@ -805,7 +1341,189 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>품목코드</v>
+      </c>
+      <c r="B1" t="str">
+        <v>품목명[규격]</v>
+      </c>
+      <c r="C1" t="str">
+        <v>대분류</v>
+      </c>
+      <c r="D1" t="str">
+        <v>재고수량</v>
+      </c>
+      <c r="E1" t="str">
+        <v>완제품단가</v>
+      </c>
+      <c r="F1" t="str">
+        <v>반제품단가</v>
+      </c>
+      <c r="G1" t="str">
+        <v>재고*완제품단가</v>
+      </c>
+      <c r="H1" t="str">
+        <v>재고*반제품단가</v>
+      </c>
+      <c r="I1" t="str">
+        <v>고객사</v>
+      </c>
+      <c r="J1" t="str">
+        <v>잔량분석</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SF-201</v>
+      </c>
+      <c r="B2" t="str">
+        <v>예시반제품 다 [SUB]</v>
+      </c>
+      <c r="C2" t="str">
+        <v>반제품</v>
+      </c>
+      <c r="D2">
+        <v>260</v>
+      </c>
+      <c r="E2">
+        <v>3750</v>
+      </c>
+      <c r="F2">
+        <v>2500</v>
+      </c>
+      <c r="G2">
+        <v>975000</v>
+      </c>
+      <c r="H2">
+        <v>650000</v>
+      </c>
+      <c r="I2" t="str">
+        <v>예시고객사 3</v>
+      </c>
+      <c r="J2" t="str">
+        <v>12개월초과</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SF-202</v>
+      </c>
+      <c r="B3" t="str">
+        <v>예시반제품 라 [SUB]</v>
+      </c>
+      <c r="C3" t="str">
+        <v>반제품</v>
+      </c>
+      <c r="D3">
+        <v>90</v>
+      </c>
+      <c r="E3">
+        <v>6000</v>
+      </c>
+      <c r="F3">
+        <v>4000</v>
+      </c>
+      <c r="G3">
+        <v>540000</v>
+      </c>
+      <c r="H3">
+        <v>360000</v>
+      </c>
+      <c r="I3" t="str">
+        <v>예시고객사 1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>품목코드</v>
+      </c>
+      <c r="B1" t="str">
+        <v>품목명[규격]</v>
+      </c>
+      <c r="C1" t="str">
+        <v>대분류</v>
+      </c>
+      <c r="D1" t="str">
+        <v>재고수량</v>
+      </c>
+      <c r="E1" t="str">
+        <v>완제품단가</v>
+      </c>
+      <c r="F1" t="str">
+        <v>반제품단가</v>
+      </c>
+      <c r="G1" t="str">
+        <v>재고*완제품단가</v>
+      </c>
+      <c r="H1" t="str">
+        <v>재고*반제품단가</v>
+      </c>
+      <c r="I1" t="str">
+        <v>고객사</v>
+      </c>
+      <c r="J1" t="str">
+        <v>잔량분석</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SF-201</v>
+      </c>
+      <c r="B2" t="str">
+        <v>예시반제품 다 [SUB]</v>
+      </c>
+      <c r="C2" t="str">
+        <v>반제품</v>
+      </c>
+      <c r="D2">
+        <v>300</v>
+      </c>
+      <c r="E2">
+        <v>3750</v>
+      </c>
+      <c r="F2">
+        <v>2500</v>
+      </c>
+      <c r="G2">
+        <v>1125000</v>
+      </c>
+      <c r="H2">
+        <v>750000</v>
+      </c>
+      <c r="I2" t="str">
+        <v>예시고객사 3</v>
+      </c>
+      <c r="J2" t="str">
+        <v>12개월</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <sheetData>
@@ -894,7 +1612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <sheetData>

--- a/samples/예시데이터_8월재고분석현황(대구).xlsx
+++ b/samples/예시데이터_8월재고분석현황(대구).xlsx
@@ -756,7 +756,7 @@
         <v>300</v>
       </c>
       <c r="C4">
-        <v>750000</v>
+        <v>7500000</v>
       </c>
       <c r="D4">
         <v>260</v>
@@ -796,7 +796,7 @@
         <v>300</v>
       </c>
       <c r="C6">
-        <v>750000</v>
+        <v>7500000</v>
       </c>
       <c r="D6">
         <v>350</v>

--- a/samples/예시데이터_8월재고분석현황(대구).xlsx
+++ b/samples/예시데이터_8월재고분석현황(대구).xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="원자재" sheetId="1" r:id="rId1"/>
-    <sheet name="반제품" sheetId="2" r:id="rId2"/>
-    <sheet name="제품" sheetId="3" r:id="rId3"/>
-    <sheet name="대구 8월 원자재" sheetId="4" r:id="rId4"/>
-    <sheet name="대구 7월 원자재" sheetId="5" r:id="rId5"/>
-    <sheet name="대구 8월 반제품" sheetId="6" r:id="rId6"/>
-    <sheet name="대구 7월 반제품" sheetId="7" r:id="rId7"/>
-    <sheet name="대구 8월 제품" sheetId="8" r:id="rId8"/>
-    <sheet name="대구 7월 제품" sheetId="9" r:id="rId9"/>
+    <sheet name="총괄현황" sheetId="1" r:id="rId1"/>
+    <sheet name="원자재" sheetId="2" r:id="rId2"/>
+    <sheet name="반제품" sheetId="3" r:id="rId3"/>
+    <sheet name="제품" sheetId="4" r:id="rId4"/>
+    <sheet name="대구 8월 원자재" sheetId="5" r:id="rId5"/>
+    <sheet name="대구 7월 원자재" sheetId="6" r:id="rId6"/>
+    <sheet name="대구 8월 반제품" sheetId="7" r:id="rId7"/>
+    <sheet name="대구 7월 반제품" sheetId="8" r:id="rId8"/>
+    <sheet name="대구 8월 제품" sheetId="9" r:id="rId9"/>
+    <sheet name="대구 7월 제품" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -405,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:F9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -417,135 +418,78 @@
         <v>구분</v>
       </c>
       <c r="B2" t="str">
-        <v>대분류</v>
+        <v>항목</v>
       </c>
       <c r="C2" t="str">
-        <v>재고현황(07월)</v>
+        <v>26년 07월</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>26년 08월</v>
       </c>
       <c r="E2" t="str">
-        <v>재고현황(08월)</v>
+        <v>증감</v>
       </c>
       <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>수량 증감 비교 (08월재고현황 - 07월재고현황)</v>
-      </c>
-      <c r="H2" t="str">
-        <v>금액 증감 비교 (08월재고현황 - 07월재고현황)</v>
-      </c>
-      <c r="I2" t="str">
-        <v>원인분석</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
         <v>비고</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>자재</v>
       </c>
       <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v xml:space="preserve"> 수량</v>
-      </c>
-      <c r="D3" t="str">
-        <v>금액</v>
-      </c>
-      <c r="E3" t="str">
-        <v xml:space="preserve"> 수량</v>
+        <v>정상</v>
+      </c>
+      <c r="C3">
+        <v>4.4</v>
+      </c>
+      <c r="D3">
+        <v>4.8</v>
+      </c>
+      <c r="E3">
+        <v>0.4</v>
       </c>
       <c r="F3" t="str">
-        <v>금액</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>07월 재고현황</v>
-      </c>
-      <c r="J3" t="str">
-        <v>08월 재고현황</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>원자재</v>
+        <v/>
       </c>
       <c r="B4" t="str">
-        <v>하우징류</v>
+        <v>불용</v>
       </c>
       <c r="C4">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4200</v>
-      </c>
-      <c r="F4">
-        <v>504000</v>
-      </c>
-      <c r="G4">
-        <v>-800</v>
-      </c>
-      <c r="H4">
-        <v>-96000</v>
-      </c>
-      <c r="I4" t="str">
-        <v>1종</v>
-      </c>
-      <c r="J4" t="str">
-        <v>1종</v>
-      </c>
-      <c r="K4" t="str">
+        <v>0</v>
+      </c>
+      <c r="F4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>반제품</v>
       </c>
       <c r="B5" t="str">
-        <v>터미널류</v>
+        <v>정상</v>
       </c>
       <c r="C5">
-        <v>30000</v>
+        <v>0.8</v>
       </c>
       <c r="D5">
-        <v>1350000</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>28000</v>
-      </c>
-      <c r="F5">
-        <v>1260000</v>
-      </c>
-      <c r="G5">
-        <v>-2000</v>
-      </c>
-      <c r="H5">
-        <v>-90000</v>
-      </c>
-      <c r="I5" t="str">
-        <v>1종</v>
-      </c>
-      <c r="J5" t="str">
-        <v>1종</v>
-      </c>
-      <c r="K5" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="F5" t="str">
         <v/>
       </c>
     </row>
@@ -554,68 +498,38 @@
         <v/>
       </c>
       <c r="B6" t="str">
-        <v>와이어류</v>
+        <v>불용</v>
       </c>
       <c r="C6">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1260000</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>9000</v>
-      </c>
-      <c r="F6">
-        <v>1620000</v>
-      </c>
-      <c r="G6">
-        <v>2000</v>
-      </c>
-      <c r="H6">
-        <v>360000</v>
-      </c>
-      <c r="I6" t="str">
-        <v>1종</v>
-      </c>
-      <c r="J6" t="str">
-        <v>1종</v>
-      </c>
-      <c r="K6" t="str">
+        <v>0</v>
+      </c>
+      <c r="F6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>제품</v>
       </c>
       <c r="B7" t="str">
-        <v>스위치</v>
+        <v>정상</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="D7">
-        <v>1000000</v>
+        <v>3.4</v>
       </c>
       <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>1250000</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>250000</v>
-      </c>
-      <c r="I7" t="str">
-        <v>1종</v>
-      </c>
-      <c r="J7" t="str">
-        <v>1종</v>
-      </c>
-      <c r="K7" t="str">
+        <v>-0.4</v>
+      </c>
+      <c r="F7" t="str">
         <v/>
       </c>
     </row>
@@ -624,81 +538,140 @@
         <v/>
       </c>
       <c r="B8" t="str">
-        <v>기타</v>
+        <v>불용</v>
       </c>
       <c r="C8">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>186000</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>600</v>
-      </c>
-      <c r="F8">
-        <v>186000</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8" t="str">
-        <v>1종</v>
-      </c>
-      <c r="J8" t="str">
-        <v>1종</v>
-      </c>
-      <c r="K8" t="str">
+        <v>0</v>
+      </c>
+      <c r="F8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v>계</v>
       </c>
       <c r="B9" t="str">
-        <v>합계</v>
-      </c>
-      <c r="C9">
-        <v>42620</v>
-      </c>
-      <c r="D9">
-        <v>4396000</v>
-      </c>
-      <c r="E9">
-        <v>41825</v>
-      </c>
-      <c r="F9">
-        <v>4820000</v>
-      </c>
-      <c r="G9">
-        <v>-795</v>
-      </c>
-      <c r="H9">
-        <v>424000</v>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>품목코드</v>
+      </c>
+      <c r="B1" t="str">
+        <v>품목명[규격]</v>
+      </c>
+      <c r="C1" t="str">
+        <v>대분류</v>
+      </c>
+      <c r="D1" t="str">
+        <v>재고수량</v>
+      </c>
+      <c r="E1" t="str">
+        <v>완제품단가</v>
+      </c>
+      <c r="F1" t="str">
+        <v>재고*완제품단가</v>
+      </c>
+      <c r="G1" t="str">
+        <v>고객사</v>
+      </c>
+      <c r="H1" t="str">
+        <v>잔량분석</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>FG-507</v>
+      </c>
+      <c r="B2" t="str">
+        <v>예시제품 사</v>
+      </c>
+      <c r="C2" t="str">
+        <v>완제품</v>
+      </c>
+      <c r="D2">
+        <v>75</v>
+      </c>
+      <c r="E2">
+        <v>27000</v>
+      </c>
+      <c r="F2">
+        <v>2025000</v>
+      </c>
+      <c r="G2" t="str">
+        <v>예시고객사 3</v>
+      </c>
+      <c r="H2" t="str">
+        <v>12개월</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>FG-601</v>
+      </c>
+      <c r="B3" t="str">
+        <v>예시제품 아</v>
+      </c>
+      <c r="C3" t="str">
+        <v>완제품</v>
+      </c>
+      <c r="D3">
+        <v>200</v>
+      </c>
+      <c r="E3">
+        <v>9000</v>
+      </c>
+      <c r="F3">
+        <v>1800000</v>
+      </c>
+      <c r="G3" t="str">
+        <v>예시고객사 1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:K9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -710,22 +683,34 @@
         <v>구분</v>
       </c>
       <c r="B2" t="str">
-        <v>07월 재고현황</v>
+        <v>대분류</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>재고현황(07월)</v>
       </c>
       <c r="D2" t="str">
-        <v>08월 재고현황</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>재고현황(08월)</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>재고잔량분석</v>
+        <v>수량 증감 비교 (08월재고현황 - 07월재고현황)</v>
+      </c>
+      <c r="H2" t="str">
+        <v>금액 증감 비교 (08월재고현황 - 07월재고현황)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>원인분석</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>비고</v>
       </c>
     </row>
     <row r="3">
@@ -733,84 +718,246 @@
         <v/>
       </c>
       <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
         <v xml:space="preserve"> 수량</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>금액</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v xml:space="preserve"> 수량</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>금액</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>07월 재고현황</v>
+      </c>
+      <c r="J3" t="str">
+        <v>08월 재고현황</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>예시고객사 3</v>
-      </c>
-      <c r="B4">
-        <v>300</v>
+        <v>원자재</v>
+      </c>
+      <c r="B4" t="str">
+        <v>하우징류</v>
       </c>
       <c r="C4">
-        <v>7500000</v>
+        <v>5000</v>
       </c>
       <c r="D4">
-        <v>260</v>
+        <v>600000</v>
       </c>
       <c r="E4">
-        <v>650000</v>
-      </c>
-      <c r="F4" t="str">
+        <v>4200</v>
+      </c>
+      <c r="F4">
+        <v>504000</v>
+      </c>
+      <c r="G4">
+        <v>-800</v>
+      </c>
+      <c r="H4">
+        <v>-96000</v>
+      </c>
+      <c r="I4" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J4" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>예시고객사 1</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v>터미널류</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="D5">
-        <v>90</v>
+        <v>1350000</v>
       </c>
       <c r="E5">
-        <v>360000</v>
-      </c>
-      <c r="F5" t="str">
+        <v>28000</v>
+      </c>
+      <c r="F5">
+        <v>1260000</v>
+      </c>
+      <c r="G5">
+        <v>-2000</v>
+      </c>
+      <c r="H5">
+        <v>-90000</v>
+      </c>
+      <c r="I5" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J5" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>총합계</v>
-      </c>
-      <c r="B6">
-        <v>300</v>
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v>와이어류</v>
       </c>
       <c r="C6">
-        <v>7500000</v>
+        <v>7000</v>
       </c>
       <c r="D6">
-        <v>350</v>
+        <v>1260000</v>
       </c>
       <c r="E6">
-        <v>1010000</v>
-      </c>
-      <c r="F6" t="str">
+        <v>9000</v>
+      </c>
+      <c r="F6">
+        <v>1620000</v>
+      </c>
+      <c r="G6">
+        <v>2000</v>
+      </c>
+      <c r="H6">
+        <v>360000</v>
+      </c>
+      <c r="I6" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J6" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v>스위치</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>1000000</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>1250000</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>250000</v>
+      </c>
+      <c r="I7" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J7" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v>기타</v>
+      </c>
+      <c r="C8">
+        <v>600</v>
+      </c>
+      <c r="D8">
+        <v>186000</v>
+      </c>
+      <c r="E8">
+        <v>600</v>
+      </c>
+      <c r="F8">
+        <v>186000</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <v>1종</v>
+      </c>
+      <c r="J8" t="str">
+        <v>1종</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v>합계</v>
+      </c>
+      <c r="C9">
+        <v>42620</v>
+      </c>
+      <c r="D9">
+        <v>4396000</v>
+      </c>
+      <c r="E9">
+        <v>41825</v>
+      </c>
+      <c r="F9">
+        <v>4820000</v>
+      </c>
+      <c r="G9">
+        <v>-795</v>
+      </c>
+      <c r="H9">
+        <v>424000</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -872,16 +1019,16 @@
         <v>예시고객사 3</v>
       </c>
       <c r="B4">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="C4">
-        <v>2025000</v>
+        <v>7500000</v>
       </c>
       <c r="D4">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="E4">
-        <v>2025000</v>
+        <v>650000</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -892,16 +1039,16 @@
         <v>예시고객사 1</v>
       </c>
       <c r="B5">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1800000</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="E5">
-        <v>1350000</v>
+        <v>360000</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -912,16 +1059,16 @@
         <v>총합계</v>
       </c>
       <c r="B6">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="C6">
-        <v>3825000</v>
+        <v>7500000</v>
       </c>
       <c r="D6">
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="E6">
-        <v>3375000</v>
+        <v>1010000</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -936,6 +1083,125 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>대구기준</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>구분</v>
+      </c>
+      <c r="B2" t="str">
+        <v>07월 재고현황</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>08월 재고현황</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>재고잔량분석</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="C3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="D3" t="str">
+        <v xml:space="preserve"> 수량</v>
+      </c>
+      <c r="E3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>예시고객사 3</v>
+      </c>
+      <c r="B4">
+        <v>75</v>
+      </c>
+      <c r="C4">
+        <v>2025000</v>
+      </c>
+      <c r="D4">
+        <v>75</v>
+      </c>
+      <c r="E4">
+        <v>2025000</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>예시고객사 1</v>
+      </c>
+      <c r="B5">
+        <v>200</v>
+      </c>
+      <c r="C5">
+        <v>1800000</v>
+      </c>
+      <c r="D5">
+        <v>150</v>
+      </c>
+      <c r="E5">
+        <v>1350000</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>총합계</v>
+      </c>
+      <c r="B6">
+        <v>275</v>
+      </c>
+      <c r="C6">
+        <v>3825000</v>
+      </c>
+      <c r="D6">
+        <v>225</v>
+      </c>
+      <c r="E6">
+        <v>3375000</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I7"/>
   <sheetData>
     <row r="1">
@@ -1148,7 +1414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H7"/>
   <sheetData>
@@ -1341,7 +1607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J3"/>
   <sheetData>
@@ -1448,7 +1714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J2"/>
   <sheetData>
@@ -1519,95 +1785,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>품목코드</v>
-      </c>
-      <c r="B1" t="str">
-        <v>품목명[규격]</v>
-      </c>
-      <c r="C1" t="str">
-        <v>대분류</v>
-      </c>
-      <c r="D1" t="str">
-        <v>재고수량</v>
-      </c>
-      <c r="E1" t="str">
-        <v>완제품단가</v>
-      </c>
-      <c r="F1" t="str">
-        <v>재고*완제품단가</v>
-      </c>
-      <c r="G1" t="str">
-        <v>고객사</v>
-      </c>
-      <c r="H1" t="str">
-        <v>잔량분석</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>FG-507</v>
-      </c>
-      <c r="B2" t="str">
-        <v>예시제품 사</v>
-      </c>
-      <c r="C2" t="str">
-        <v>완제품</v>
-      </c>
-      <c r="D2">
-        <v>75</v>
-      </c>
-      <c r="E2">
-        <v>27000</v>
-      </c>
-      <c r="F2">
-        <v>2025000</v>
-      </c>
-      <c r="G2" t="str">
-        <v>예시고객사 3</v>
-      </c>
-      <c r="H2" t="str">
-        <v>12개월초과</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>FG-601</v>
-      </c>
-      <c r="B3" t="str">
-        <v>예시제품 아</v>
-      </c>
-      <c r="C3" t="str">
-        <v>완제품</v>
-      </c>
-      <c r="D3">
-        <v>150</v>
-      </c>
-      <c r="E3">
-        <v>9000</v>
-      </c>
-      <c r="F3">
-        <v>1350000</v>
-      </c>
-      <c r="G3" t="str">
-        <v>예시고객사 1</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1665,7 +1842,7 @@
         <v>예시고객사 3</v>
       </c>
       <c r="H2" t="str">
-        <v>12개월</v>
+        <v>12개월초과</v>
       </c>
     </row>
     <row r="3">
@@ -1679,13 +1856,13 @@
         <v>완제품</v>
       </c>
       <c r="D3">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E3">
         <v>9000</v>
       </c>
       <c r="F3">
-        <v>1800000</v>
+        <v>1350000</v>
       </c>
       <c r="G3" t="str">
         <v>예시고객사 1</v>
